--- a/Performance Evaluation Results.xlsx
+++ b/Performance Evaluation Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bed2753ba2ca735/Desktop/Kandi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2032" documentId="11_AD4D4B9C664837EAC52650FFAC13C9E4693EDF17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED0E235A-D0B9-4622-A676-AD10D84A2AF9}"/>
+  <xr:revisionPtr revIDLastSave="2199" documentId="11_AD4D4B9C664837EAC52650FFAC13C9E4693EDF17" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18FD898F-EB0C-4BFD-AF6A-4185DB47AB15}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="29">
   <si>
     <t>Python</t>
   </si>
@@ -97,6 +97,33 @@
   <si>
     <t>Range</t>
   </si>
+  <si>
+    <t>Data values for each file:</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Readability</t>
+  </si>
+  <si>
+    <t>Learning curve</t>
+  </si>
+  <si>
+    <t>Community support</t>
+  </si>
+  <si>
+    <t>Type safety</t>
+  </si>
+  <si>
+    <t>Average score</t>
+  </si>
+  <si>
+    <t>Libraries and features</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
 </sst>
 </file>
 
@@ -114,7 +141,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,6 +178,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -164,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -173,6 +224,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -5911,6 +5966,723 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fi-FI"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fi-FI" baseline="0"/>
+              <a:t>Productivity</a:t>
+            </a:r>
+            <a:endParaRPr lang="fi-FI"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fi-FI"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Python</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Taul1!$BL$2:$BP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Readability</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Learning curve</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Libraries and features</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Community support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Type safety</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Taul1!$BL$3:$BP$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1052-48C3-96C6-3CD6A54DEFAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>C++</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Taul1!$BL$2:$BP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Readability</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Learning curve</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Libraries and features</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Community support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Type safety</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Taul1!$BL$4:$BP$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1052-48C3-96C6-3CD6A54DEFAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Java</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Taul1!$BL$2:$BP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Readability</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Learning curve</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Libraries and features</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Community support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Type safety</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Taul1!$BL$5:$BP$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1052-48C3-96C6-3CD6A54DEFAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Go</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Taul1!$BL$2:$BP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Readability</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Learning curve</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Libraries and features</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Community support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Type safety</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Taul1!$BL$6:$BP$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1052-48C3-96C6-3CD6A54DEFAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Rust</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Taul1!$BL$2:$BP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Readability</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Learning curve</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Libraries and features</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Community support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Type safety</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Taul1!$BL$7:$BP$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-1052-48C3-96C6-3CD6A54DEFAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>Julia</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Taul1!$BL$2:$BP$2</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Readability</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Learning curve</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Libraries and features</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Community support</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Type safety</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Taul1!$BL$8:$BP$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-1052-48C3-96C6-3CD6A54DEFAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1055708495"/>
+        <c:axId val="1055706575"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="1055708495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fi-FI"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1055706575"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1055706575"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fi-FI"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1055708495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fi-FI"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fi-FI"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -6151,6 +6923,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -9228,6 +10040,511 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -9470,6 +10787,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>212725</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>434975</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Kaavio 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FD557DF-F9B8-5461-0D88-95692762A78B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -9745,10 +11098,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BQ37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="63" max="63" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="12.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:69" x14ac:dyDescent="0.35">
       <c r="E1" s="5"/>
       <c r="F1" s="5" t="s">
         <v>0</v>
@@ -9779,8 +11141,11 @@
         <v>11</v>
       </c>
       <c r="BE1" s="5"/>
+      <c r="BN1" s="11" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
@@ -9877,8 +11242,29 @@
         <v>3</v>
       </c>
       <c r="BH2" s="3"/>
+      <c r="BK2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="BL2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="BM2" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BN2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="BP2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="BQ2" s="9" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
@@ -10059,8 +11445,30 @@
       <c r="BH3" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="BK3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="10">
+        <v>5</v>
+      </c>
+      <c r="BM3" s="10">
+        <v>5</v>
+      </c>
+      <c r="BN3" s="10">
+        <v>5</v>
+      </c>
+      <c r="BO3" s="10">
+        <v>5</v>
+      </c>
+      <c r="BP3" s="10">
+        <v>3</v>
+      </c>
+      <c r="BQ3" s="10">
+        <f t="shared" ref="BQ3:BQ8" si="0">AVERAGE(BL3:BP3)</f>
+        <v>4.5999999999999996</v>
+      </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -10259,8 +11667,30 @@
         <f>BF4+BG4</f>
         <v>22.662299999999998</v>
       </c>
+      <c r="BK4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="BL4" s="10">
+        <v>3</v>
+      </c>
+      <c r="BM4" s="10">
+        <v>3</v>
+      </c>
+      <c r="BN4" s="10">
+        <v>4</v>
+      </c>
+      <c r="BO4" s="10">
+        <v>4</v>
+      </c>
+      <c r="BP4" s="10">
+        <v>3</v>
+      </c>
+      <c r="BQ4" s="10">
+        <f t="shared" si="0"/>
+        <v>3.4</v>
+      </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -10281,7 +11711,7 @@
         <v>0.14485999999999999</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:G23" si="0">E5+F5</f>
+        <f t="shared" ref="G5:G23" si="1">E5+F5</f>
         <v>0.47371999999999997</v>
       </c>
       <c r="H5" s="3">
@@ -10291,7 +11721,7 @@
         <v>6.91798</v>
       </c>
       <c r="J5" s="3">
-        <f t="shared" ref="J5:J23" si="1">H5+I5</f>
+        <f t="shared" ref="J5:J23" si="2">H5+I5</f>
         <v>24.924949999999999</v>
       </c>
       <c r="K5" s="4">
@@ -10304,7 +11734,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="N5" s="1">
-        <f t="shared" ref="N5:N23" si="2">L5+M5</f>
+        <f t="shared" ref="N5:N23" si="3">L5+M5</f>
         <v>1.2600000000000001E-3</v>
       </c>
       <c r="O5" s="2">
@@ -10314,7 +11744,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
       <c r="Q5" s="2">
-        <f t="shared" ref="Q5:Q23" si="3">O5+P5</f>
+        <f t="shared" ref="Q5:Q23" si="4">O5+P5</f>
         <v>5.5779999999999996E-2</v>
       </c>
       <c r="R5" s="3">
@@ -10324,7 +11754,7 @@
         <v>0.27261999999999997</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" ref="T5:T23" si="4">R5+S5</f>
+        <f t="shared" ref="T5:T23" si="5">R5+S5</f>
         <v>3.1585799999999997</v>
       </c>
       <c r="U5" s="4">
@@ -10337,7 +11767,7 @@
         <v>1.8500000000000001E-3</v>
       </c>
       <c r="X5" s="1">
-        <f t="shared" ref="X5:X23" si="5">V5+W5</f>
+        <f t="shared" ref="X5:X23" si="6">V5+W5</f>
         <v>2.4310000000000002E-2</v>
       </c>
       <c r="Y5" s="2">
@@ -10347,7 +11777,7 @@
         <v>2.1479999999999999E-2</v>
       </c>
       <c r="AA5" s="2">
-        <f t="shared" ref="AA5:AA23" si="6">Y5+Z5</f>
+        <f t="shared" ref="AA5:AA23" si="7">Y5+Z5</f>
         <v>0.15736</v>
       </c>
       <c r="AB5" s="3">
@@ -10357,7 +11787,7 @@
         <v>0.42585000000000001</v>
       </c>
       <c r="AD5" s="3">
-        <f t="shared" ref="AD5:AD23" si="7">AB5+AC5</f>
+        <f t="shared" ref="AD5:AD23" si="8">AB5+AC5</f>
         <v>4.7510599999999998</v>
       </c>
       <c r="AE5" s="4">
@@ -10370,7 +11800,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="AH5" s="1">
-        <f t="shared" ref="AH5:AH23" si="8">AF5+AG5</f>
+        <f t="shared" ref="AH5:AH23" si="9">AF5+AG5</f>
         <v>2.99E-3</v>
       </c>
       <c r="AI5" s="2">
@@ -10380,7 +11810,7 @@
         <v>4.6499999999999996E-3</v>
       </c>
       <c r="AK5" s="2">
-        <f t="shared" ref="AK5:AK23" si="9">AI5+AJ5</f>
+        <f t="shared" ref="AK5:AK23" si="10">AI5+AJ5</f>
         <v>7.5499999999999998E-2</v>
       </c>
       <c r="AL5" s="3">
@@ -10390,7 +11820,7 @@
         <v>0.28838000000000003</v>
       </c>
       <c r="AN5" s="3">
-        <f t="shared" ref="AN5:AN23" si="10">AL5+AM5</f>
+        <f t="shared" ref="AN5:AN23" si="11">AL5+AM5</f>
         <v>3.7217899999999999</v>
       </c>
       <c r="AO5" s="4">
@@ -10403,7 +11833,7 @@
         <v>1.1E-4</v>
       </c>
       <c r="AR5" s="1">
-        <f t="shared" ref="AR5:AR23" si="11">AP5+AQ5</f>
+        <f t="shared" ref="AR5:AR23" si="12">AP5+AQ5</f>
         <v>1.8000000000000002E-3</v>
       </c>
       <c r="AS5" s="2">
@@ -10413,7 +11843,7 @@
         <v>5.5300000000000002E-3</v>
       </c>
       <c r="AU5" s="2">
-        <f t="shared" ref="AU5:AU23" si="12">AS5+AT5</f>
+        <f t="shared" ref="AU5:AU23" si="13">AS5+AT5</f>
         <v>6.878999999999999E-2</v>
       </c>
       <c r="AV5" s="3">
@@ -10423,7 +11853,7 @@
         <v>0.32885999999999999</v>
       </c>
       <c r="AX5" s="3">
-        <f t="shared" ref="AX5:AX23" si="13">AV5+AW5</f>
+        <f t="shared" ref="AX5:AX23" si="14">AV5+AW5</f>
         <v>4.0863800000000001</v>
       </c>
       <c r="AY5" s="4">
@@ -10436,7 +11866,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="BB5" s="1">
-        <f t="shared" ref="BB5:BB23" si="14">AZ5+BA5</f>
+        <f t="shared" ref="BB5:BB23" si="15">AZ5+BA5</f>
         <v>6.9199999999999999E-3</v>
       </c>
       <c r="BC5" s="2">
@@ -10446,7 +11876,7 @@
         <v>1.6800000000000001E-3</v>
       </c>
       <c r="BE5" s="2">
-        <f t="shared" ref="BE5:BE23" si="15">BC5+BD5</f>
+        <f t="shared" ref="BE5:BE23" si="16">BC5+BD5</f>
         <v>0.44729000000000002</v>
       </c>
       <c r="BF5" s="3">
@@ -10456,11 +11886,33 @@
         <v>0.10421999999999999</v>
       </c>
       <c r="BH5" s="3">
-        <f t="shared" ref="BH5:BH23" si="16">BF5+BG5</f>
+        <f t="shared" ref="BH5:BH23" si="17">BF5+BG5</f>
         <v>22.319600000000001</v>
       </c>
+      <c r="BK5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL5" s="10">
+        <v>3</v>
+      </c>
+      <c r="BM5" s="10">
+        <v>3</v>
+      </c>
+      <c r="BN5" s="10">
+        <v>5</v>
+      </c>
+      <c r="BO5" s="10">
+        <v>5</v>
+      </c>
+      <c r="BP5" s="10">
+        <v>4</v>
+      </c>
+      <c r="BQ5" s="10">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -10471,7 +11923,7 @@
         <v>1.5299999999999999E-3</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D23" si="17">B6+C6</f>
+        <f t="shared" ref="D6:D23" si="18">B6+C6</f>
         <v>5.77E-3</v>
       </c>
       <c r="E6" s="2">
@@ -10481,7 +11933,7 @@
         <v>0.14760000000000001</v>
       </c>
       <c r="G6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.49085000000000001</v>
       </c>
       <c r="H6" s="3">
@@ -10491,7 +11943,7 @@
         <v>8.2223299999999995</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.524339999999999</v>
       </c>
       <c r="K6" s="4">
@@ -10504,7 +11956,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="N6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="O6" s="2">
@@ -10514,7 +11966,7 @@
         <v>4.47E-3</v>
       </c>
       <c r="Q6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.4800000000000001E-2</v>
       </c>
       <c r="R6" s="3">
@@ -10524,7 +11976,7 @@
         <v>0.27439999999999998</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1769099999999999</v>
       </c>
       <c r="U6" s="4">
@@ -10537,7 +11989,7 @@
         <v>2.2399999999999998E-3</v>
       </c>
       <c r="X6" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.9519999999999998E-2</v>
       </c>
       <c r="Y6" s="2">
@@ -10547,7 +11999,7 @@
         <v>2.0029999999999999E-2</v>
       </c>
       <c r="AA6" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13833999999999999</v>
       </c>
       <c r="AB6" s="3">
@@ -10557,7 +12009,7 @@
         <v>0.41996</v>
       </c>
       <c r="AD6" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8393499999999996</v>
       </c>
       <c r="AE6" s="4">
@@ -10570,7 +12022,7 @@
         <v>5.4000000000000001E-4</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4.0699999999999998E-3</v>
       </c>
       <c r="AI6" s="2">
@@ -10580,7 +12032,7 @@
         <v>7.4799999999999997E-3</v>
       </c>
       <c r="AK6" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.10979</v>
       </c>
       <c r="AL6" s="3">
@@ -10590,7 +12042,7 @@
         <v>0.29148000000000002</v>
       </c>
       <c r="AN6" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7006399999999999</v>
       </c>
       <c r="AO6" s="4">
@@ -10603,7 +12055,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="AR6" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.47E-3</v>
       </c>
       <c r="AS6" s="2">
@@ -10613,7 +12065,7 @@
         <v>5.2700000000000004E-3</v>
       </c>
       <c r="AU6" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.8879999999999997E-2</v>
       </c>
       <c r="AV6" s="3">
@@ -10623,7 +12075,7 @@
         <v>0.32002000000000003</v>
       </c>
       <c r="AX6" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9891299999999998</v>
       </c>
       <c r="AY6" s="4">
@@ -10636,7 +12088,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB6" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1399999999999996E-3</v>
       </c>
       <c r="BC6" s="2">
@@ -10646,7 +12098,7 @@
         <v>1.74E-3</v>
       </c>
       <c r="BE6" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.46004</v>
       </c>
       <c r="BF6" s="3">
@@ -10656,11 +12108,33 @@
         <v>0.10067</v>
       </c>
       <c r="BH6" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>23.165459999999999</v>
       </c>
+      <c r="BK6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BL6" s="10">
+        <v>4</v>
+      </c>
+      <c r="BM6" s="10">
+        <v>4</v>
+      </c>
+      <c r="BN6" s="10">
+        <v>4</v>
+      </c>
+      <c r="BO6" s="10">
+        <v>3</v>
+      </c>
+      <c r="BP6" s="10">
+        <v>4</v>
+      </c>
+      <c r="BQ6" s="10">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -10671,7 +12145,7 @@
         <v>1.5499999999999999E-3</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.2700000000000004E-3</v>
       </c>
       <c r="E7" s="2">
@@ -10681,7 +12155,7 @@
         <v>0.15448000000000001</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.49292999999999998</v>
       </c>
       <c r="H7" s="3">
@@ -10691,7 +12165,7 @@
         <v>8.3542000000000005</v>
       </c>
       <c r="J7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25.822000000000003</v>
       </c>
       <c r="K7" s="4">
@@ -10704,7 +12178,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.23E-3</v>
       </c>
       <c r="O7" s="2">
@@ -10714,7 +12188,7 @@
         <v>4.6699999999999997E-3</v>
       </c>
       <c r="Q7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.7680000000000002E-2</v>
       </c>
       <c r="R7" s="3">
@@ -10724,7 +12198,7 @@
         <v>0.27256000000000002</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2429899999999998</v>
       </c>
       <c r="U7" s="4">
@@ -10737,7 +12211,7 @@
         <v>2.2499999999999998E-3</v>
       </c>
       <c r="X7" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0009999999999998E-2</v>
       </c>
       <c r="Y7" s="2">
@@ -10747,7 +12221,7 @@
         <v>2.0740000000000001E-2</v>
       </c>
       <c r="AA7" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14418</v>
       </c>
       <c r="AB7" s="3">
@@ -10757,7 +12231,7 @@
         <v>0.38064999999999999</v>
       </c>
       <c r="AD7" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.7733699999999999</v>
       </c>
       <c r="AE7" s="4">
@@ -10770,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="AH7" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.4399999999999999E-3</v>
       </c>
       <c r="AI7" s="2">
@@ -10780,7 +12254,7 @@
         <v>1.136E-2</v>
       </c>
       <c r="AK7" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.9039999999999999E-2</v>
       </c>
       <c r="AL7" s="3">
@@ -10790,7 +12264,7 @@
         <v>0.29494999999999999</v>
       </c>
       <c r="AN7" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7119599999999999</v>
       </c>
       <c r="AO7" s="4">
@@ -10803,7 +12277,7 @@
         <v>1.3999999999999999E-4</v>
       </c>
       <c r="AR7" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3799999999999999E-3</v>
       </c>
       <c r="AS7" s="2">
@@ -10813,7 +12287,7 @@
         <v>5.2500000000000003E-3</v>
       </c>
       <c r="AU7" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.9880000000000012E-2</v>
       </c>
       <c r="AV7" s="3">
@@ -10823,7 +12297,7 @@
         <v>0.33511999999999997</v>
       </c>
       <c r="AX7" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0206999999999997</v>
       </c>
       <c r="AY7" s="4">
@@ -10836,7 +12310,7 @@
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="BB7" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.9999999999999993E-3</v>
       </c>
       <c r="BC7" s="2">
@@ -10846,7 +12320,7 @@
         <v>1.8E-3</v>
       </c>
       <c r="BE7" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.46040000000000003</v>
       </c>
       <c r="BF7" s="3">
@@ -10856,11 +12330,33 @@
         <v>0.10199999999999999</v>
       </c>
       <c r="BH7" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.954789999999999</v>
       </c>
+      <c r="BK7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL7" s="10">
+        <v>2</v>
+      </c>
+      <c r="BM7" s="10">
+        <v>2</v>
+      </c>
+      <c r="BN7" s="10">
+        <v>3</v>
+      </c>
+      <c r="BO7" s="10">
+        <v>3</v>
+      </c>
+      <c r="BP7" s="10">
+        <v>5</v>
+      </c>
+      <c r="BQ7" s="10">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -10871,7 +12367,7 @@
         <v>1.5100000000000001E-3</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.7099999999999998E-3</v>
       </c>
       <c r="E8" s="2">
@@ -10881,7 +12377,7 @@
         <v>0.14807000000000001</v>
       </c>
       <c r="G8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.44728999999999997</v>
       </c>
       <c r="H8" s="3">
@@ -10891,7 +12387,7 @@
         <v>7.4148399999999999</v>
       </c>
       <c r="J8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.693770000000001</v>
       </c>
       <c r="K8" s="4">
@@ -10904,7 +12400,7 @@
         <v>1E-4</v>
       </c>
       <c r="N8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.99E-3</v>
       </c>
       <c r="O8" s="2">
@@ -10914,7 +12410,7 @@
         <v>5.2900000000000004E-3</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.9710000000000006E-2</v>
       </c>
       <c r="R8" s="3">
@@ -10924,7 +12420,7 @@
         <v>0.27295000000000003</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1896199999999997</v>
       </c>
       <c r="U8" s="4">
@@ -10937,7 +12433,7 @@
         <v>1.89E-3</v>
       </c>
       <c r="X8" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.911E-2</v>
       </c>
       <c r="Y8" s="2">
@@ -10947,7 +12443,7 @@
         <v>1.9470000000000001E-2</v>
       </c>
       <c r="AA8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13800000000000001</v>
       </c>
       <c r="AB8" s="3">
@@ -10957,7 +12453,7 @@
         <v>0.42464000000000002</v>
       </c>
       <c r="AD8" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8651299999999997</v>
       </c>
       <c r="AE8" s="4">
@@ -10970,7 +12466,7 @@
         <v>0</v>
       </c>
       <c r="AH8" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.9699999999999996E-3</v>
       </c>
       <c r="AI8" s="2">
@@ -10980,7 +12476,7 @@
         <v>5.7000000000000002E-3</v>
       </c>
       <c r="AK8" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.782E-2</v>
       </c>
       <c r="AL8" s="3">
@@ -10990,7 +12486,7 @@
         <v>0.31161</v>
       </c>
       <c r="AN8" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7952499999999998</v>
       </c>
       <c r="AO8" s="4">
@@ -11003,7 +12499,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR8" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.32E-3</v>
       </c>
       <c r="AS8" s="2">
@@ -11013,7 +12509,7 @@
         <v>5.5900000000000004E-3</v>
       </c>
       <c r="AU8" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.9999999999999993E-2</v>
       </c>
       <c r="AV8" s="3">
@@ -11023,7 +12519,7 @@
         <v>0.33413999999999999</v>
       </c>
       <c r="AX8" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0629099999999996</v>
       </c>
       <c r="AY8" s="4">
@@ -11036,7 +12532,7 @@
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="BB8" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.0699999999999999E-3</v>
       </c>
       <c r="BC8" s="2">
@@ -11046,7 +12542,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="BE8" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.45293999999999995</v>
       </c>
       <c r="BF8" s="3">
@@ -11056,11 +12552,33 @@
         <v>0.10732</v>
       </c>
       <c r="BH8" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.397200000000002</v>
       </c>
+      <c r="BK8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="BL8" s="10">
+        <v>5</v>
+      </c>
+      <c r="BM8" s="10">
+        <v>4</v>
+      </c>
+      <c r="BN8" s="10">
+        <v>3</v>
+      </c>
+      <c r="BO8" s="10">
+        <v>2</v>
+      </c>
+      <c r="BP8" s="10">
+        <v>4</v>
+      </c>
+      <c r="BQ8" s="10">
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -11071,7 +12589,7 @@
         <v>1.6800000000000001E-3</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.3099999999999996E-3</v>
       </c>
       <c r="E9" s="2">
@@ -11081,7 +12599,7 @@
         <v>9.5280000000000004E-2</v>
       </c>
       <c r="G9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.34787999999999997</v>
       </c>
       <c r="H9" s="3">
@@ -11091,7 +12609,7 @@
         <v>7.4993999999999996</v>
       </c>
       <c r="J9" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25.660020000000003</v>
       </c>
       <c r="K9" s="4">
@@ -11104,7 +12622,7 @@
         <v>1.1E-4</v>
       </c>
       <c r="N9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.5100000000000001E-3</v>
       </c>
       <c r="O9" s="2">
@@ -11114,7 +12632,7 @@
         <v>4.7999999999999996E-3</v>
       </c>
       <c r="Q9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.7409999999999996E-2</v>
       </c>
       <c r="R9" s="3">
@@ -11124,7 +12642,7 @@
         <v>0.28187000000000001</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.17761</v>
       </c>
       <c r="U9" s="4">
@@ -11137,7 +12655,7 @@
         <v>2.5600000000000002E-3</v>
       </c>
       <c r="X9" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.15E-2</v>
       </c>
       <c r="Y9" s="2">
@@ -11147,7 +12665,7 @@
         <v>2.0150000000000001E-2</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13535</v>
       </c>
       <c r="AB9" s="3">
@@ -11157,7 +12675,7 @@
         <v>0.38177</v>
       </c>
       <c r="AD9" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8463700000000003</v>
       </c>
       <c r="AE9" s="4">
@@ -11170,7 +12688,7 @@
         <v>0</v>
       </c>
       <c r="AH9" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.2699999999999999E-3</v>
       </c>
       <c r="AI9" s="2">
@@ -11180,7 +12698,7 @@
         <v>1.0120000000000001E-2</v>
       </c>
       <c r="AK9" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4750000000000011E-2</v>
       </c>
       <c r="AL9" s="3">
@@ -11190,7 +12708,7 @@
         <v>0.28766000000000003</v>
       </c>
       <c r="AN9" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6624999999999996</v>
       </c>
       <c r="AO9" s="4">
@@ -11203,7 +12721,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR9" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.5300000000000001E-3</v>
       </c>
       <c r="AS9" s="2">
@@ -11213,7 +12731,7 @@
         <v>6.2500000000000003E-3</v>
       </c>
       <c r="AU9" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.0760000000000003E-2</v>
       </c>
       <c r="AV9" s="3">
@@ -11223,7 +12741,7 @@
         <v>0.33005000000000001</v>
       </c>
       <c r="AX9" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.948</v>
       </c>
       <c r="AY9" s="4">
@@ -11236,7 +12754,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="BB9" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.8399999999999997E-3</v>
       </c>
       <c r="BC9" s="2">
@@ -11246,7 +12764,7 @@
         <v>1.73E-3</v>
       </c>
       <c r="BE9" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.45400000000000001</v>
       </c>
       <c r="BF9" s="3">
@@ -11256,11 +12774,11 @@
         <v>9.9890000000000007E-2</v>
       </c>
       <c r="BH9" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.756349999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -11271,7 +12789,7 @@
         <v>2.48E-3</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.2200000000000008E-3</v>
       </c>
       <c r="E10" s="2">
@@ -11281,7 +12799,7 @@
         <v>0.14468</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.48140000000000005</v>
       </c>
       <c r="H10" s="3">
@@ -11291,7 +12809,7 @@
         <v>7.9499300000000002</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.264360000000003</v>
       </c>
       <c r="K10" s="4">
@@ -11304,7 +12822,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.15E-3</v>
       </c>
       <c r="O10" s="2">
@@ -11314,7 +12832,7 @@
         <v>5.0600000000000003E-3</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6070000000000002E-2</v>
       </c>
       <c r="R10" s="3">
@@ -11324,7 +12842,7 @@
         <v>0.27252999999999999</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2160200000000003</v>
       </c>
       <c r="U10" s="4">
@@ -11337,7 +12855,7 @@
         <v>2.0600000000000002E-3</v>
       </c>
       <c r="X10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0669999999999999E-2</v>
       </c>
       <c r="Y10" s="2">
@@ -11347,7 +12865,7 @@
         <v>2.2290000000000001E-2</v>
       </c>
       <c r="AA10" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14657999999999999</v>
       </c>
       <c r="AB10" s="3">
@@ -11357,7 +12875,7 @@
         <v>0.39137</v>
       </c>
       <c r="AD10" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8149300000000004</v>
       </c>
       <c r="AE10" s="4">
@@ -11370,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="AH10" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.7100000000000002E-3</v>
       </c>
       <c r="AI10" s="2">
@@ -11380,7 +12898,7 @@
         <v>5.3E-3</v>
       </c>
       <c r="AK10" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.349E-2</v>
       </c>
       <c r="AL10" s="3">
@@ -11390,7 +12908,7 @@
         <v>0.28855999999999998</v>
       </c>
       <c r="AN10" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.66988</v>
       </c>
       <c r="AO10" s="4">
@@ -11403,7 +12921,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="AR10" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.2199999999999999E-3</v>
       </c>
       <c r="AS10" s="2">
@@ -11413,7 +12931,7 @@
         <v>5.2100000000000002E-3</v>
       </c>
       <c r="AU10" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.1570000000000009E-2</v>
       </c>
       <c r="AV10" s="3">
@@ -11423,7 +12941,7 @@
         <v>0.34569</v>
       </c>
       <c r="AX10" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0721699999999998</v>
       </c>
       <c r="AY10" s="4">
@@ -11436,7 +12954,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB10" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.8700000000000002E-3</v>
       </c>
       <c r="BC10" s="2">
@@ -11446,7 +12964,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="BE10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44795999999999997</v>
       </c>
       <c r="BF10" s="3">
@@ -11456,11 +12974,11 @@
         <v>9.98E-2</v>
       </c>
       <c r="BH10" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.373189999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -11471,7 +12989,7 @@
         <v>1.8699999999999999E-3</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>6.9500000000000004E-3</v>
       </c>
       <c r="E11" s="2">
@@ -11481,7 +12999,7 @@
         <v>0.11101</v>
       </c>
       <c r="G11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.40183999999999997</v>
       </c>
       <c r="H11" s="3">
@@ -11491,7 +13009,7 @@
         <v>7.3788900000000002</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25.892209999999999</v>
       </c>
       <c r="K11" s="4">
@@ -11504,7 +13022,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="N11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="O11" s="2">
@@ -11514,7 +13032,7 @@
         <v>5.3200000000000001E-3</v>
       </c>
       <c r="Q11" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6119999999999996E-2</v>
       </c>
       <c r="R11" s="3">
@@ -11524,7 +13042,7 @@
         <v>0.27242</v>
       </c>
       <c r="T11" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2032400000000001</v>
       </c>
       <c r="U11" s="4">
@@ -11537,7 +13055,7 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="X11" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.53E-2</v>
       </c>
       <c r="Y11" s="2">
@@ -11547,7 +13065,7 @@
         <v>1.9259999999999999E-2</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13206000000000001</v>
       </c>
       <c r="AB11" s="3">
@@ -11557,7 +13075,7 @@
         <v>0.44063000000000002</v>
       </c>
       <c r="AD11" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8706999999999994</v>
       </c>
       <c r="AE11" s="4">
@@ -11570,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="AH11" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6199999999999999E-3</v>
       </c>
       <c r="AI11" s="2">
@@ -11580,7 +13098,7 @@
         <v>7.4000000000000003E-3</v>
       </c>
       <c r="AK11" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4060000000000001E-2</v>
       </c>
       <c r="AL11" s="3">
@@ -11590,7 +13108,7 @@
         <v>0.28721999999999998</v>
       </c>
       <c r="AN11" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6949100000000001</v>
       </c>
       <c r="AO11" s="4">
@@ -11603,7 +13121,7 @@
         <v>1.2E-4</v>
       </c>
       <c r="AR11" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4500000000000001E-3</v>
       </c>
       <c r="AS11" s="2">
@@ -11613,7 +13131,7 @@
         <v>5.1999999999999998E-3</v>
       </c>
       <c r="AU11" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.7549999999999999E-2</v>
       </c>
       <c r="AV11" s="3">
@@ -11623,7 +13141,7 @@
         <v>0.33302999999999999</v>
       </c>
       <c r="AX11" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.94835</v>
       </c>
       <c r="AY11" s="4">
@@ -11636,7 +13154,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB11" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.9100000000000003E-3</v>
       </c>
       <c r="BC11" s="2">
@@ -11646,7 +13164,7 @@
         <v>1.6900000000000001E-3</v>
       </c>
       <c r="BE11" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44443000000000005</v>
       </c>
       <c r="BF11" s="3">
@@ -11656,11 +13174,11 @@
         <v>0.10054</v>
       </c>
       <c r="BH11" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.424979999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -11671,7 +13189,7 @@
         <v>1.6100000000000001E-3</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8600000000000006E-3</v>
       </c>
       <c r="E12" s="2">
@@ -11681,7 +13199,7 @@
         <v>9.6640000000000004E-2</v>
       </c>
       <c r="G12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.36046</v>
       </c>
       <c r="H12" s="3">
@@ -11691,7 +13209,7 @@
         <v>8.0905000000000005</v>
       </c>
       <c r="J12" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.115070000000003</v>
       </c>
       <c r="K12" s="4">
@@ -11704,7 +13222,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1299999999999999E-3</v>
       </c>
       <c r="O12" s="2">
@@ -11714,7 +13232,7 @@
         <v>6.0099999999999997E-3</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8369999999999998E-2</v>
       </c>
       <c r="R12" s="3">
@@ -11724,7 +13242,7 @@
         <v>0.27706999999999998</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1824500000000002</v>
       </c>
       <c r="U12" s="4">
@@ -11737,7 +13255,7 @@
         <v>1.8500000000000001E-3</v>
       </c>
       <c r="X12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.8310000000000002E-2</v>
       </c>
       <c r="Y12" s="2">
@@ -11747,7 +13265,7 @@
         <v>2.0369999999999999E-2</v>
       </c>
       <c r="AA12" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13567000000000001</v>
       </c>
       <c r="AB12" s="3">
@@ -11757,7 +13275,7 @@
         <v>0.44836999999999999</v>
       </c>
       <c r="AD12" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.9015899999999997</v>
       </c>
       <c r="AE12" s="4">
@@ -11770,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.7699999999999999E-3</v>
       </c>
       <c r="AI12" s="2">
@@ -11780,7 +13298,7 @@
         <v>6.2899999999999996E-3</v>
       </c>
       <c r="AK12" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.5550000000000006E-2</v>
       </c>
       <c r="AL12" s="3">
@@ -11790,7 +13308,7 @@
         <v>0.30312</v>
       </c>
       <c r="AN12" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.6893799999999999</v>
       </c>
       <c r="AO12" s="4">
@@ -11803,7 +13321,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR12" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.4300000000000001E-3</v>
       </c>
       <c r="AS12" s="2">
@@ -11813,7 +13331,7 @@
         <v>6.0499999999999998E-3</v>
       </c>
       <c r="AU12" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.9309999999999997E-2</v>
       </c>
       <c r="AV12" s="3">
@@ -11823,7 +13341,7 @@
         <v>0.33818999999999999</v>
       </c>
       <c r="AX12" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.1068999999999996</v>
       </c>
       <c r="AY12" s="4">
@@ -11836,7 +13354,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB12" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.8399999999999997E-3</v>
       </c>
       <c r="BC12" s="2">
@@ -11846,7 +13364,7 @@
         <v>1.73E-3</v>
       </c>
       <c r="BE12" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.45351000000000002</v>
       </c>
       <c r="BF12" s="3">
@@ -11856,11 +13374,11 @@
         <v>9.9769999999999998E-2</v>
       </c>
       <c r="BH12" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.618169999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -11871,7 +13389,7 @@
         <v>1.57E-3</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8799999999999998E-3</v>
       </c>
       <c r="E13" s="2">
@@ -11881,7 +13399,7 @@
         <v>0.14308000000000001</v>
       </c>
       <c r="G13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.46865999999999997</v>
       </c>
       <c r="H13" s="3">
@@ -11891,7 +13409,7 @@
         <v>8.4041800000000002</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.18159</v>
       </c>
       <c r="K13" s="4">
@@ -11904,7 +13422,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="N13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999999E-3</v>
       </c>
       <c r="O13" s="2">
@@ -11914,7 +13432,7 @@
         <v>4.5500000000000002E-3</v>
       </c>
       <c r="Q13" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6439999999999997E-2</v>
       </c>
       <c r="R13" s="3">
@@ -11924,7 +13442,7 @@
         <v>0.28145999999999999</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.3521299999999998</v>
       </c>
       <c r="U13" s="4">
@@ -11937,7 +13455,7 @@
         <v>3.0599999999999998E-3</v>
       </c>
       <c r="X13" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.1579999999999997E-2</v>
       </c>
       <c r="Y13" s="2">
@@ -11947,7 +13465,7 @@
         <v>2.0910000000000002E-2</v>
       </c>
       <c r="AA13" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13836000000000001</v>
       </c>
       <c r="AB13" s="3">
@@ -11957,7 +13475,7 @@
         <v>0.37206</v>
       </c>
       <c r="AD13" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.7956799999999999</v>
       </c>
       <c r="AE13" s="4">
@@ -11970,7 +13488,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.7499999999999998E-3</v>
       </c>
       <c r="AI13" s="2">
@@ -11980,7 +13498,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="AK13" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.6819999999999999E-2</v>
       </c>
       <c r="AL13" s="3">
@@ -11990,7 +13508,7 @@
         <v>0.33407999999999999</v>
       </c>
       <c r="AN13" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7500300000000002</v>
       </c>
       <c r="AO13" s="4">
@@ -12003,7 +13521,7 @@
         <v>1.1E-4</v>
       </c>
       <c r="AR13" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3900000000000002E-3</v>
       </c>
       <c r="AS13" s="2">
@@ -12013,7 +13531,7 @@
         <v>5.96E-3</v>
       </c>
       <c r="AU13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.8700000000000011E-2</v>
       </c>
       <c r="AV13" s="3">
@@ -12023,7 +13541,7 @@
         <v>0.33743000000000001</v>
       </c>
       <c r="AX13" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0034200000000002</v>
       </c>
       <c r="AY13" s="4">
@@ -12036,7 +13554,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.9500000000000004E-3</v>
       </c>
       <c r="BC13" s="2">
@@ -12046,7 +13564,7 @@
         <v>1.72E-3</v>
       </c>
       <c r="BE13" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44896000000000003</v>
       </c>
       <c r="BF13" s="3">
@@ -12056,11 +13574,11 @@
         <v>0.10050000000000001</v>
       </c>
       <c r="BH13" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.636960000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -12071,7 +13589,7 @@
         <v>2.32E-3</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.150000000000001E-3</v>
       </c>
       <c r="E14" s="2">
@@ -12081,7 +13599,7 @@
         <v>0.14265</v>
       </c>
       <c r="G14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.46971000000000002</v>
       </c>
       <c r="H14" s="3">
@@ -12091,7 +13609,7 @@
         <v>8.3323900000000002</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.41628</v>
       </c>
       <c r="K14" s="4">
@@ -12104,7 +13622,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.4E-3</v>
       </c>
       <c r="O14" s="2">
@@ -12114,7 +13632,7 @@
         <v>5.3E-3</v>
       </c>
       <c r="Q14" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.7099999999999998E-2</v>
       </c>
       <c r="R14" s="3">
@@ -12124,7 +13642,7 @@
         <v>0.27263999999999999</v>
       </c>
       <c r="T14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1511300000000002</v>
       </c>
       <c r="U14" s="4">
@@ -12137,7 +13655,7 @@
         <v>2.2899999999999999E-3</v>
       </c>
       <c r="X14" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0329999999999999E-2</v>
       </c>
       <c r="Y14" s="2">
@@ -12147,7 +13665,7 @@
         <v>1.8720000000000001E-2</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13694000000000001</v>
       </c>
       <c r="AB14" s="3">
@@ -12157,7 +13675,7 @@
         <v>0.42568</v>
       </c>
       <c r="AD14" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8584699999999996</v>
       </c>
       <c r="AE14" s="4">
@@ -12170,7 +13688,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.2899999999999999E-3</v>
       </c>
       <c r="AI14" s="2">
@@ -12180,7 +13698,7 @@
         <v>6.94E-3</v>
       </c>
       <c r="AK14" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.6230000000000006E-2</v>
       </c>
       <c r="AL14" s="3">
@@ -12190,7 +13708,7 @@
         <v>0.30146000000000001</v>
       </c>
       <c r="AN14" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7211400000000001</v>
       </c>
       <c r="AO14" s="4">
@@ -12203,7 +13721,7 @@
         <v>1.2999999999999999E-4</v>
       </c>
       <c r="AR14" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.6599999999999998E-3</v>
       </c>
       <c r="AS14" s="2">
@@ -12213,7 +13731,7 @@
         <v>5.64E-3</v>
       </c>
       <c r="AU14" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.0230000000000001E-2</v>
       </c>
       <c r="AV14" s="3">
@@ -12223,7 +13741,7 @@
         <v>0.32967999999999997</v>
       </c>
       <c r="AX14" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9903300000000002</v>
       </c>
       <c r="AY14" s="4">
@@ -12236,7 +13754,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1200000000000005E-3</v>
       </c>
       <c r="BC14" s="2">
@@ -12246,7 +13764,7 @@
         <v>1.74E-3</v>
       </c>
       <c r="BE14" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44208000000000003</v>
       </c>
       <c r="BF14" s="3">
@@ -12256,11 +13774,11 @@
         <v>0.10191</v>
       </c>
       <c r="BH14" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.23631</v>
       </c>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -12271,7 +13789,7 @@
         <v>1.7600000000000001E-3</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.9700000000000005E-3</v>
       </c>
       <c r="E15" s="2">
@@ -12281,7 +13799,7 @@
         <v>0.10020999999999999</v>
       </c>
       <c r="G15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.43020000000000003</v>
       </c>
       <c r="H15" s="3">
@@ -12291,7 +13809,7 @@
         <v>8.6584099999999999</v>
       </c>
       <c r="J15" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28.81739</v>
       </c>
       <c r="K15" s="4">
@@ -12304,7 +13822,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.14E-3</v>
       </c>
       <c r="O15" s="2">
@@ -12314,7 +13832,7 @@
         <v>4.5100000000000001E-3</v>
       </c>
       <c r="Q15" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5780000000000003E-2</v>
       </c>
       <c r="R15" s="3">
@@ -12324,7 +13842,7 @@
         <v>0.27298</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2174499999999999</v>
       </c>
       <c r="U15" s="4">
@@ -12337,7 +13855,7 @@
         <v>1.82E-3</v>
       </c>
       <c r="X15" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.2500000000000001E-2</v>
       </c>
       <c r="Y15" s="2">
@@ -12347,7 +13865,7 @@
         <v>2.146E-2</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14230999999999999</v>
       </c>
       <c r="AB15" s="3">
@@ -12357,7 +13875,7 @@
         <v>0.41175</v>
       </c>
       <c r="AD15" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8178599999999996</v>
       </c>
       <c r="AE15" s="4">
@@ -12370,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="AH15" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.1900000000000001E-3</v>
       </c>
       <c r="AI15" s="2">
@@ -12380,7 +13898,7 @@
         <v>6.7000000000000002E-3</v>
       </c>
       <c r="AK15" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.7289999999999998E-2</v>
       </c>
       <c r="AL15" s="3">
@@ -12390,7 +13908,7 @@
         <v>0.31052999999999997</v>
       </c>
       <c r="AN15" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.73732</v>
       </c>
       <c r="AO15" s="4">
@@ -12403,7 +13921,7 @@
         <v>1.1E-4</v>
       </c>
       <c r="AR15" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3900000000000002E-3</v>
       </c>
       <c r="AS15" s="2">
@@ -12413,7 +13931,7 @@
         <v>6.28E-3</v>
       </c>
       <c r="AU15" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.109E-2</v>
       </c>
       <c r="AV15" s="3">
@@ -12423,7 +13941,7 @@
         <v>0.34033999999999998</v>
       </c>
       <c r="AX15" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9916899999999997</v>
       </c>
       <c r="AY15" s="4">
@@ -12436,7 +13954,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB15" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.0699999999999999E-3</v>
       </c>
       <c r="BC15" s="2">
@@ -12446,7 +13964,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="BE15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44403999999999999</v>
       </c>
       <c r="BF15" s="3">
@@ -12456,11 +13974,11 @@
         <v>0.10037</v>
       </c>
       <c r="BH15" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.564410000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:69" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -12471,7 +13989,7 @@
         <v>1.6100000000000001E-3</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8400000000000006E-3</v>
       </c>
       <c r="E16" s="2">
@@ -12481,7 +13999,7 @@
         <v>0.14229</v>
       </c>
       <c r="G16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.47904999999999998</v>
       </c>
       <c r="H16" s="3">
@@ -12491,7 +14009,7 @@
         <v>8.1266400000000001</v>
       </c>
       <c r="J16" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.466880000000003</v>
       </c>
       <c r="K16" s="4">
@@ -12504,7 +14022,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.09E-3</v>
       </c>
       <c r="O16" s="2">
@@ -12514,7 +14032,7 @@
         <v>5.2700000000000004E-3</v>
       </c>
       <c r="Q16" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8929999999999996E-2</v>
       </c>
       <c r="R16" s="3">
@@ -12524,7 +14042,7 @@
         <v>0.27250999999999997</v>
       </c>
       <c r="T16" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1402399999999999</v>
       </c>
       <c r="U16" s="4">
@@ -12537,7 +14055,7 @@
         <v>2.0200000000000001E-3</v>
       </c>
       <c r="X16" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.9389999999999999E-2</v>
       </c>
       <c r="Y16" s="2">
@@ -12547,7 +14065,7 @@
         <v>1.9060000000000001E-2</v>
       </c>
       <c r="AA16" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13957</v>
       </c>
       <c r="AB16" s="3">
@@ -12557,7 +14075,7 @@
         <v>0.43042999999999998</v>
       </c>
       <c r="AD16" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8613300000000006</v>
       </c>
       <c r="AE16" s="4">
@@ -12570,7 +14088,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.4499999999999999E-3</v>
       </c>
       <c r="AI16" s="2">
@@ -12580,7 +14098,7 @@
         <v>1.393E-2</v>
       </c>
       <c r="AK16" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.8599999999999998E-2</v>
       </c>
       <c r="AL16" s="3">
@@ -12590,7 +14108,7 @@
         <v>0.29559999999999997</v>
       </c>
       <c r="AN16" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.77217</v>
       </c>
       <c r="AO16" s="4">
@@ -12603,7 +14121,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.47E-3</v>
       </c>
       <c r="AS16" s="2">
@@ -12613,7 +14131,7 @@
         <v>5.5300000000000002E-3</v>
       </c>
       <c r="AU16" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.5759999999999994E-2</v>
       </c>
       <c r="AV16" s="3">
@@ -12623,7 +14141,7 @@
         <v>0.34745999999999999</v>
       </c>
       <c r="AX16" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0266299999999999</v>
       </c>
       <c r="AY16" s="4">
@@ -12636,7 +14154,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB16" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="BC16" s="2">
@@ -12646,7 +14164,7 @@
         <v>1.6900000000000001E-3</v>
       </c>
       <c r="BE16" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44257000000000002</v>
       </c>
       <c r="BF16" s="3">
@@ -12656,7 +14174,7 @@
         <v>9.9860000000000004E-2</v>
       </c>
       <c r="BH16" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.507059999999999</v>
       </c>
     </row>
@@ -12671,7 +14189,7 @@
         <v>2.7299999999999998E-3</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>1.0249999999999999E-2</v>
       </c>
       <c r="E17" s="2">
@@ -12681,7 +14199,7 @@
         <v>0.15231</v>
       </c>
       <c r="G17" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.50252999999999992</v>
       </c>
       <c r="H17" s="3">
@@ -12691,7 +14209,7 @@
         <v>8.3434500000000007</v>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.341640000000002</v>
       </c>
       <c r="K17" s="4">
@@ -12704,7 +14222,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.08E-3</v>
       </c>
       <c r="O17" s="2">
@@ -12714,7 +14232,7 @@
         <v>4.7299999999999998E-3</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.935E-2</v>
       </c>
       <c r="R17" s="3">
@@ -12724,7 +14242,7 @@
         <v>0.27639999999999998</v>
       </c>
       <c r="T17" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.1559099999999995</v>
       </c>
       <c r="U17" s="4">
@@ -12737,7 +14255,7 @@
         <v>2.2100000000000002E-3</v>
       </c>
       <c r="X17" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="Y17" s="2">
@@ -12747,7 +14265,7 @@
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="AA17" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13723000000000002</v>
       </c>
       <c r="AB17" s="3">
@@ -12757,7 +14275,7 @@
         <v>0.37940000000000002</v>
       </c>
       <c r="AD17" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8494300000000008</v>
       </c>
       <c r="AE17" s="4">
@@ -12770,7 +14288,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.4599999999999999E-3</v>
       </c>
       <c r="AI17" s="2">
@@ -12780,7 +14298,7 @@
         <v>6.6800000000000002E-3</v>
       </c>
       <c r="AK17" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.758000000000001E-2</v>
       </c>
       <c r="AL17" s="3">
@@ -12790,7 +14308,7 @@
         <v>0.30091000000000001</v>
       </c>
       <c r="AN17" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7116000000000002</v>
       </c>
       <c r="AO17" s="4">
@@ -12803,7 +14321,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="AR17" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.25E-3</v>
       </c>
       <c r="AS17" s="2">
@@ -12813,7 +14331,7 @@
         <v>5.2399999999999999E-3</v>
       </c>
       <c r="AU17" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.9169999999999995E-2</v>
       </c>
       <c r="AV17" s="3">
@@ -12823,7 +14341,7 @@
         <v>0.34005000000000002</v>
       </c>
       <c r="AX17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.04155</v>
       </c>
       <c r="AY17" s="4">
@@ -12836,7 +14354,7 @@
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="BB17" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.94E-3</v>
       </c>
       <c r="BC17" s="2">
@@ -12846,7 +14364,7 @@
         <v>1.6900000000000001E-3</v>
       </c>
       <c r="BE17" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.45088</v>
       </c>
       <c r="BF17" s="3">
@@ -12856,7 +14374,7 @@
         <v>9.9860000000000004E-2</v>
       </c>
       <c r="BH17" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.489429999999999</v>
       </c>
     </row>
@@ -12871,7 +14389,7 @@
         <v>1.5200000000000001E-3</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.7700000000000008E-3</v>
       </c>
       <c r="E18" s="2">
@@ -12881,7 +14399,7 @@
         <v>0.14768999999999999</v>
       </c>
       <c r="G18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.44114999999999999</v>
       </c>
       <c r="H18" s="3">
@@ -12891,7 +14409,7 @@
         <v>8.3466000000000005</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.650379999999998</v>
       </c>
       <c r="K18" s="4">
@@ -12904,7 +14422,7 @@
         <v>1.1E-4</v>
       </c>
       <c r="N18" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.42E-3</v>
       </c>
       <c r="O18" s="2">
@@ -12914,7 +14432,7 @@
         <v>4.5100000000000001E-3</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5640000000000002E-2</v>
       </c>
       <c r="R18" s="3">
@@ -12924,7 +14442,7 @@
         <v>0.27831</v>
       </c>
       <c r="T18" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.29467</v>
       </c>
       <c r="U18" s="4">
@@ -12937,7 +14455,7 @@
         <v>1.8699999999999999E-3</v>
       </c>
       <c r="X18" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.6839999999999999E-2</v>
       </c>
       <c r="Y18" s="2">
@@ -12947,7 +14465,7 @@
         <v>2.0330000000000001E-2</v>
       </c>
       <c r="AA18" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14096</v>
       </c>
       <c r="AB18" s="3">
@@ -12957,7 +14475,7 @@
         <v>0.45195000000000002</v>
       </c>
       <c r="AD18" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8564300000000005</v>
       </c>
       <c r="AE18" s="4">
@@ -12970,7 +14488,7 @@
         <v>5.5000000000000003E-4</v>
       </c>
       <c r="AH18" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.98E-3</v>
       </c>
       <c r="AI18" s="2">
@@ -12980,7 +14498,7 @@
         <v>4.9100000000000003E-3</v>
       </c>
       <c r="AK18" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.8339999999999993E-2</v>
       </c>
       <c r="AL18" s="3">
@@ -12990,7 +14508,7 @@
         <v>0.31313000000000002</v>
       </c>
       <c r="AN18" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7867000000000002</v>
       </c>
       <c r="AO18" s="4">
@@ -13003,7 +14521,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR18" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3700000000000001E-3</v>
       </c>
       <c r="AS18" s="2">
@@ -13013,7 +14531,7 @@
         <v>5.1700000000000001E-3</v>
       </c>
       <c r="AU18" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.83E-2</v>
       </c>
       <c r="AV18" s="3">
@@ -13023,7 +14541,7 @@
         <v>0.34969</v>
       </c>
       <c r="AX18" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.2269899999999998</v>
       </c>
       <c r="AY18" s="4">
@@ -13036,7 +14554,7 @@
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="BB18" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.9499999999999996E-3</v>
       </c>
       <c r="BC18" s="2">
@@ -13046,7 +14564,7 @@
         <v>1.83E-3</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.45838000000000001</v>
       </c>
       <c r="BF18" s="3">
@@ -13056,7 +14574,7 @@
         <v>0.10058</v>
       </c>
       <c r="BH18" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.543600000000001</v>
       </c>
     </row>
@@ -13071,7 +14589,7 @@
         <v>2.9099999999999998E-3</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>8.7299999999999999E-3</v>
       </c>
       <c r="E19" s="2">
@@ -13081,7 +14599,7 @@
         <v>9.4270000000000007E-2</v>
       </c>
       <c r="G19" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.41434000000000004</v>
       </c>
       <c r="H19" s="3">
@@ -13091,7 +14609,7 @@
         <v>7.4206799999999999</v>
       </c>
       <c r="J19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24.748380000000001</v>
       </c>
       <c r="K19" s="4">
@@ -13104,7 +14622,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N19" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.81E-3</v>
       </c>
       <c r="O19" s="2">
@@ -13114,7 +14632,7 @@
         <v>4.4799999999999996E-3</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.4349999999999996E-2</v>
       </c>
       <c r="R19" s="3">
@@ -13124,7 +14642,7 @@
         <v>0.27407999999999999</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.22384</v>
       </c>
       <c r="U19" s="4">
@@ -13137,7 +14655,7 @@
         <v>2.1299999999999999E-3</v>
       </c>
       <c r="X19" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.3439999999999998E-2</v>
       </c>
       <c r="Y19" s="2">
@@ -13147,7 +14665,7 @@
         <v>2.001E-2</v>
       </c>
       <c r="AA19" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14627000000000001</v>
       </c>
       <c r="AB19" s="3">
@@ -13157,7 +14675,7 @@
         <v>0.40027000000000001</v>
       </c>
       <c r="AD19" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8746900000000002</v>
       </c>
       <c r="AE19" s="4">
@@ -13170,7 +14688,7 @@
         <v>0</v>
       </c>
       <c r="AH19" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6099999999999999E-3</v>
       </c>
       <c r="AI19" s="2">
@@ -13180,7 +14698,7 @@
         <v>6.3E-3</v>
       </c>
       <c r="AK19" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>8.4839999999999999E-2</v>
       </c>
       <c r="AL19" s="3">
@@ -13190,7 +14708,7 @@
         <v>0.32580999999999999</v>
       </c>
       <c r="AN19" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.8093700000000004</v>
       </c>
       <c r="AO19" s="4">
@@ -13203,7 +14721,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR19" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.58E-3</v>
       </c>
       <c r="AS19" s="2">
@@ -13213,7 +14731,7 @@
         <v>5.1799999999999997E-3</v>
       </c>
       <c r="AU19" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.7570000000000005E-2</v>
       </c>
       <c r="AV19" s="3">
@@ -13223,7 +14741,7 @@
         <v>0.35949999999999999</v>
       </c>
       <c r="AX19" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.1105400000000003</v>
       </c>
       <c r="AY19" s="4">
@@ -13236,7 +14754,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB19" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.8599999999999998E-3</v>
       </c>
       <c r="BC19" s="2">
@@ -13246,7 +14764,7 @@
         <v>1.73E-3</v>
       </c>
       <c r="BE19" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44355</v>
       </c>
       <c r="BF19" s="3">
@@ -13256,7 +14774,7 @@
         <v>9.9860000000000004E-2</v>
       </c>
       <c r="BH19" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.91602</v>
       </c>
     </row>
@@ -13271,7 +14789,7 @@
         <v>2.5500000000000002E-3</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.2800000000000001E-3</v>
       </c>
       <c r="E20" s="2">
@@ -13291,7 +14809,7 @@
         <v>7.4508400000000004</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.365690000000001</v>
       </c>
       <c r="K20" s="4">
@@ -13304,7 +14822,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1100000000000001E-3</v>
       </c>
       <c r="O20" s="2">
@@ -13314,7 +14832,7 @@
         <v>5.1799999999999997E-3</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="R20" s="3">
@@ -13324,7 +14842,7 @@
         <v>0.27582000000000001</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2013099999999999</v>
       </c>
       <c r="U20" s="4">
@@ -13337,7 +14855,7 @@
         <v>2.3400000000000001E-3</v>
       </c>
       <c r="X20" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0199999999999998E-2</v>
       </c>
       <c r="Y20" s="2">
@@ -13347,7 +14865,7 @@
         <v>2.1420000000000002E-2</v>
       </c>
       <c r="AA20" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14122000000000001</v>
       </c>
       <c r="AB20" s="3">
@@ -13357,7 +14875,7 @@
         <v>0.39393</v>
       </c>
       <c r="AD20" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8654200000000003</v>
       </c>
       <c r="AE20" s="4">
@@ -13370,7 +14888,7 @@
         <v>0</v>
       </c>
       <c r="AH20" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.5100000000000001E-3</v>
       </c>
       <c r="AI20" s="2">
@@ -13380,7 +14898,7 @@
         <v>7.8700000000000003E-3</v>
       </c>
       <c r="AK20" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.8600000000000003E-2</v>
       </c>
       <c r="AL20" s="3">
@@ -13390,7 +14908,7 @@
         <v>0.30259999999999998</v>
       </c>
       <c r="AN20" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.706</v>
       </c>
       <c r="AO20" s="4">
@@ -13403,7 +14921,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="AR20" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3500000000000001E-3</v>
       </c>
       <c r="AS20" s="2">
@@ -13413,7 +14931,7 @@
         <v>6.6699999999999997E-3</v>
       </c>
       <c r="AU20" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.3599999999999999E-2</v>
       </c>
       <c r="AV20" s="3">
@@ -13423,7 +14941,7 @@
         <v>0.31184000000000001</v>
       </c>
       <c r="AX20" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.1458199999999996</v>
       </c>
       <c r="AY20" s="4">
@@ -13436,7 +14954,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB20" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.9199999999999999E-3</v>
       </c>
       <c r="BC20" s="2">
@@ -13446,7 +14964,7 @@
         <v>1.73E-3</v>
       </c>
       <c r="BE20" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.46606000000000003</v>
       </c>
       <c r="BF20" s="3">
@@ -13456,7 +14974,7 @@
         <v>0.10036</v>
       </c>
       <c r="BH20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.512539999999998</v>
       </c>
     </row>
@@ -13471,7 +14989,7 @@
         <v>1.56E-3</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8699999999999994E-3</v>
       </c>
       <c r="E21" s="2">
@@ -13481,7 +14999,7 @@
         <v>0.1396</v>
       </c>
       <c r="G21" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.41177000000000002</v>
       </c>
       <c r="H21" s="3">
@@ -13491,7 +15009,7 @@
         <v>8.0369200000000003</v>
       </c>
       <c r="J21" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27.104460000000003</v>
       </c>
       <c r="K21" s="4">
@@ -13504,7 +15022,7 @@
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="N21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1100000000000001E-3</v>
       </c>
       <c r="O21" s="2">
@@ -13514,7 +15032,7 @@
         <v>4.7499999999999999E-3</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6709999999999997E-2</v>
       </c>
       <c r="R21" s="3">
@@ -13524,7 +15042,7 @@
         <v>0.27476</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.24851</v>
       </c>
       <c r="U21" s="4">
@@ -13537,7 +15055,7 @@
         <v>1.97E-3</v>
       </c>
       <c r="X21" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.9089999999999998E-2</v>
       </c>
       <c r="Y21" s="2">
@@ -13547,7 +15065,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="AA21" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12812999999999999</v>
       </c>
       <c r="AB21" s="3">
@@ -13557,7 +15075,7 @@
         <v>0.42896000000000001</v>
       </c>
       <c r="AD21" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.9641999999999999</v>
       </c>
       <c r="AE21" s="4">
@@ -13570,7 +15088,7 @@
         <v>5.9000000000000003E-4</v>
       </c>
       <c r="AH21" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.15E-3</v>
       </c>
       <c r="AI21" s="2">
@@ -13580,7 +15098,7 @@
         <v>5.7400000000000003E-3</v>
       </c>
       <c r="AK21" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="AL21" s="3">
@@ -13590,7 +15108,7 @@
         <v>0.32567000000000002</v>
       </c>
       <c r="AN21" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7449500000000002</v>
       </c>
       <c r="AO21" s="4">
@@ -13603,7 +15121,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="AR21" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.23E-3</v>
       </c>
       <c r="AS21" s="2">
@@ -13613,7 +15131,7 @@
         <v>5.3299999999999997E-3</v>
       </c>
       <c r="AU21" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.8199999999999997E-2</v>
       </c>
       <c r="AV21" s="3">
@@ -13623,7 +15141,7 @@
         <v>0.31196000000000002</v>
       </c>
       <c r="AX21" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9946100000000002</v>
       </c>
       <c r="AY21" s="4">
@@ -13636,7 +15154,7 @@
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="BB21" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1200000000000005E-3</v>
       </c>
       <c r="BC21" s="2">
@@ -13646,7 +15164,7 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="BE21" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.44688999999999995</v>
       </c>
       <c r="BF21" s="3">
@@ -13656,7 +15174,7 @@
         <v>0.10005</v>
       </c>
       <c r="BH21" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.407160000000001</v>
       </c>
     </row>
@@ -13681,7 +15199,7 @@
         <v>0.14183999999999999</v>
       </c>
       <c r="G22" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.47028999999999999</v>
       </c>
       <c r="H22" s="3">
@@ -13691,7 +15209,7 @@
         <v>7.9131099999999996</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.81456</v>
       </c>
       <c r="K22" s="4">
@@ -13704,7 +15222,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="O22" s="2">
@@ -13714,7 +15232,7 @@
         <v>5.2599999999999999E-3</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8970000000000002E-2</v>
       </c>
       <c r="R22" s="3">
@@ -13724,7 +15242,7 @@
         <v>0.28234999999999999</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.2867299999999999</v>
       </c>
       <c r="U22" s="4">
@@ -13737,7 +15255,7 @@
         <v>2.4499999999999999E-3</v>
       </c>
       <c r="X22" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0079999999999999E-2</v>
       </c>
       <c r="Y22" s="2">
@@ -13747,7 +15265,7 @@
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="AA22" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15198</v>
       </c>
       <c r="AB22" s="3">
@@ -13757,7 +15275,7 @@
         <v>0.35034999999999999</v>
       </c>
       <c r="AD22" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.7673699999999997</v>
       </c>
       <c r="AE22" s="4">
@@ -13770,7 +15288,7 @@
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="AH22" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.6899999999999997E-3</v>
       </c>
       <c r="AI22" s="2">
@@ -13780,7 +15298,7 @@
         <v>5.4400000000000004E-3</v>
       </c>
       <c r="AK22" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.7239999999999994E-2</v>
       </c>
       <c r="AL22" s="3">
@@ -13790,7 +15308,7 @@
         <v>0.28797</v>
       </c>
       <c r="AN22" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.7227200000000003</v>
       </c>
       <c r="AO22" s="4">
@@ -13803,7 +15321,7 @@
         <v>1.1E-4</v>
       </c>
       <c r="AR22" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.3500000000000001E-3</v>
       </c>
       <c r="AS22" s="2">
@@ -13813,7 +15331,7 @@
         <v>5.4099999999999999E-3</v>
       </c>
       <c r="AU22" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.8409999999999999E-2</v>
       </c>
       <c r="AV22" s="3">
@@ -13823,7 +15341,7 @@
         <v>0.31969999999999998</v>
       </c>
       <c r="AX22" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9179200000000001</v>
       </c>
       <c r="AY22" s="4">
@@ -13836,7 +15354,7 @@
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB22" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>7.1999999999999998E-3</v>
       </c>
       <c r="BC22" s="2">
@@ -13846,7 +15364,7 @@
         <v>1.7899999999999999E-3</v>
       </c>
       <c r="BE22" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.47148000000000001</v>
       </c>
       <c r="BF22" s="3">
@@ -13856,7 +15374,7 @@
         <v>0.10084</v>
       </c>
       <c r="BH22" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>23.564140000000002</v>
       </c>
     </row>
@@ -13871,7 +15389,7 @@
         <v>1.5100000000000001E-3</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.8399999999999997E-3</v>
       </c>
       <c r="E23" s="2">
@@ -13881,7 +15399,7 @@
         <v>0.11852</v>
       </c>
       <c r="G23" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.41863</v>
       </c>
       <c r="H23" s="3">
@@ -13891,7 +15409,7 @@
         <v>7.3168499999999996</v>
       </c>
       <c r="J23" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26.318369999999998</v>
       </c>
       <c r="K23" s="4">
@@ -13904,7 +15422,7 @@
         <v>9.0000000000000006E-5</v>
       </c>
       <c r="N23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1000000000000001E-3</v>
       </c>
       <c r="O23" s="2">
@@ -13914,7 +15432,7 @@
         <v>4.8300000000000001E-3</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.6059999999999999E-2</v>
       </c>
       <c r="R23" s="3">
@@ -13924,7 +15442,7 @@
         <v>0.27267999999999998</v>
       </c>
       <c r="T23" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.3064799999999996</v>
       </c>
       <c r="U23" s="4">
@@ -13937,7 +15455,7 @@
         <v>1.9599999999999999E-3</v>
       </c>
       <c r="X23" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.9139999999999999E-2</v>
       </c>
       <c r="Y23" s="2">
@@ -13947,7 +15465,7 @@
         <v>2.1870000000000001E-2</v>
       </c>
       <c r="AA23" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14157999999999998</v>
       </c>
       <c r="AB23" s="3">
@@ -13957,7 +15475,7 @@
         <v>0.43994</v>
       </c>
       <c r="AD23" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4.8225699999999998</v>
       </c>
       <c r="AE23" s="4">
@@ -13970,7 +15488,7 @@
         <v>0</v>
       </c>
       <c r="AH23" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.7899999999999999E-3</v>
       </c>
       <c r="AI23" s="2">
@@ -13980,7 +15498,7 @@
         <v>2.7599999999999999E-3</v>
       </c>
       <c r="AK23" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>7.4800000000000005E-2</v>
       </c>
       <c r="AL23" s="3">
@@ -13990,7 +15508,7 @@
         <v>0.31862000000000001</v>
       </c>
       <c r="AN23" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3.91554</v>
       </c>
       <c r="AO23" s="4">
@@ -14003,7 +15521,7 @@
         <v>1E-4</v>
       </c>
       <c r="AR23" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.23E-3</v>
       </c>
       <c r="AS23" s="2">
@@ -14013,7 +15531,7 @@
         <v>5.45E-3</v>
       </c>
       <c r="AU23" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.8449999999999997E-2</v>
       </c>
       <c r="AV23" s="3">
@@ -14023,7 +15541,7 @@
         <v>0.33511999999999997</v>
       </c>
       <c r="AX23" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.91316</v>
       </c>
       <c r="AY23" s="4">
@@ -14036,7 +15554,7 @@
         <v>3.0000000000000001E-5</v>
       </c>
       <c r="BB23" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>6.8599999999999998E-3</v>
       </c>
       <c r="BC23" s="2">
@@ -14046,7 +15564,7 @@
         <v>1.75E-3</v>
       </c>
       <c r="BE23" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.45462999999999998</v>
       </c>
       <c r="BF23" s="3">
@@ -14056,7 +15574,7 @@
         <v>9.9879999999999997E-2</v>
       </c>
       <c r="BH23" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>22.441959999999998</v>
       </c>
     </row>
@@ -14073,31 +15591,31 @@
         <v>1.885E-3</v>
       </c>
       <c r="D25" s="6">
-        <f t="shared" ref="D25:J25" si="18">AVERAGE(D4:D23)</f>
+        <f t="shared" ref="D25:J25" si="19">AVERAGE(D4:D23)</f>
         <v>6.8605000000000003E-3</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.31371700000000002</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13153150000000002</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.44524850000000005</v>
       </c>
       <c r="H25" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18.757879000000003</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.8503400000000001</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>26.608219000000002</v>
       </c>
       <c r="K25" s="6"/>
@@ -14106,35 +15624,35 @@
         <v>1.1820000000000001E-3</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" ref="M25:T25" si="19">AVERAGE(M4:M23)</f>
+        <f t="shared" ref="M25:T25" si="20">AVERAGE(M4:M23)</f>
         <v>8.9500000000000007E-5</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.2715000000000001E-3</v>
       </c>
       <c r="O25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.2142500000000001E-2</v>
       </c>
       <c r="P25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.8985000000000001E-3</v>
       </c>
       <c r="Q25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.7041000000000008E-2</v>
       </c>
       <c r="R25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.9450260000000004</v>
       </c>
       <c r="S25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.27536600000000006</v>
       </c>
       <c r="T25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.2203919999999995</v>
       </c>
       <c r="U25" s="6"/>
@@ -14143,35 +15661,35 @@
         <v>2.7472999999999997E-2</v>
       </c>
       <c r="W25" s="6">
-        <f t="shared" ref="W25:AD25" si="20">AVERAGE(W4:W23)</f>
+        <f t="shared" ref="W25:AD25" si="21">AVERAGE(W4:W23)</f>
         <v>2.1780000000000002E-3</v>
       </c>
       <c r="X25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.9651000000000004E-2</v>
       </c>
       <c r="Y25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.12008450000000001</v>
       </c>
       <c r="Z25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.0552000000000001E-2</v>
       </c>
       <c r="AA25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.1406365</v>
       </c>
       <c r="AB25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.4299575000000004</v>
       </c>
       <c r="AC25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.41354749999999996</v>
       </c>
       <c r="AD25" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.8435050000000004</v>
       </c>
       <c r="AE25" s="6"/>
@@ -14184,31 +15702,31 @@
         <v>1.4399999999999998E-4</v>
       </c>
       <c r="AH25" s="6">
-        <f t="shared" ref="AH25:AN25" si="21">AVERAGE(AH4:AH23)</f>
+        <f t="shared" ref="AH25:AN25" si="22">AVERAGE(AH4:AH23)</f>
         <v>2.9019999999999992E-3</v>
       </c>
       <c r="AI25" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.1687500000000015E-2</v>
       </c>
       <c r="AJ25" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.9610000000000002E-3</v>
       </c>
       <c r="AK25" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.8648499999999996E-2</v>
       </c>
       <c r="AL25" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.4372114999999992</v>
       </c>
       <c r="AM25" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.30394499999999997</v>
       </c>
       <c r="AN25" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.7411564999999998</v>
       </c>
       <c r="AO25" s="6"/>
@@ -14217,35 +15735,35 @@
         <v>1.3035E-3</v>
       </c>
       <c r="AQ25" s="6">
-        <f t="shared" ref="AQ25:AX25" si="22">AVERAGE(AQ4:AQ23)</f>
+        <f t="shared" ref="AQ25:AX25" si="23">AVERAGE(AQ4:AQ23)</f>
         <v>1.0300000000000001E-4</v>
       </c>
       <c r="AR25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1.4065E-3</v>
       </c>
       <c r="AS25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.4180500000000001E-2</v>
       </c>
       <c r="AT25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.5949999999999984E-3</v>
       </c>
       <c r="AU25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>6.977549999999999E-2</v>
       </c>
       <c r="AV25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>3.6977494999999996</v>
       </c>
       <c r="AW25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.33370649999999996</v>
       </c>
       <c r="AX25" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>4.0314559999999995</v>
       </c>
       <c r="AY25" s="6"/>
@@ -14254,35 +15772,35 @@
         <v>6.9544999999999997E-3</v>
       </c>
       <c r="BA25" s="6">
-        <f t="shared" ref="BA25:BH25" si="23">AVERAGE(BA4:BA23)</f>
+        <f t="shared" ref="BA25:BH25" si="24">AVERAGE(BA4:BA23)</f>
         <v>2.7500000000000008E-5</v>
       </c>
       <c r="BB25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6.9820000000000004E-3</v>
       </c>
       <c r="BC25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.44990350000000001</v>
       </c>
       <c r="BD25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1.7285000000000002E-3</v>
       </c>
       <c r="BE25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.45163200000000003</v>
       </c>
       <c r="BF25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22.523646000000003</v>
       </c>
       <c r="BG25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.10093550000000003</v>
       </c>
       <c r="BH25" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>22.624581500000001</v>
       </c>
     </row>
@@ -14291,224 +15809,224 @@
         <v>13</v>
       </c>
       <c r="B26" s="6">
-        <f t="shared" ref="B26:J26" si="24">STDEV(B4:B23)</f>
+        <f t="shared" ref="B26:J26" si="25">STDEV(B4:B23)</f>
         <v>1.0357071065346204E-3</v>
       </c>
       <c r="C26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.7793965705878995E-4</v>
       </c>
       <c r="D26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.4850003544213646E-3</v>
       </c>
       <c r="E26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.8184647762100629E-2</v>
       </c>
       <c r="F26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.2611782041786429E-2</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.5303539105971784E-2</v>
       </c>
       <c r="H26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.69095297097102371</v>
       </c>
       <c r="I26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.52982066574703535</v>
       </c>
       <c r="J26" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.95651832903944989</v>
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="6">
-        <f t="shared" ref="L26:T26" si="25">STDEV(L4:L23)</f>
+        <f t="shared" ref="L26:T26" si="26">STDEV(L4:L23)</f>
         <v>2.4699456631568575E-4</v>
       </c>
       <c r="M26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>8.870412083230169E-6</v>
       </c>
       <c r="N26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2.5096183396138775E-4</v>
       </c>
       <c r="O26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.3579042482327033E-3</v>
       </c>
       <c r="P26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4.1893693784952516E-4</v>
       </c>
       <c r="Q26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.5689114563590702E-3</v>
       </c>
       <c r="R26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.7474559900789771E-2</v>
       </c>
       <c r="S26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>3.3471722550928208E-3</v>
       </c>
       <c r="T26" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>5.8843675472882329E-2</v>
       </c>
       <c r="U26" s="6"/>
       <c r="V26" s="6">
-        <f t="shared" ref="V26:AD26" si="26">STDEV(V4:V23)</f>
+        <f t="shared" ref="V26:AD26" si="27">STDEV(V4:V23)</f>
         <v>2.1454973659663203E-3</v>
       </c>
       <c r="W26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.104597609319036E-4</v>
       </c>
       <c r="X26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2.2402817022113882E-3</v>
       </c>
       <c r="Y26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.2568761963812357E-3</v>
       </c>
       <c r="Z26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1.022373914501261E-3</v>
       </c>
       <c r="AA26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.5634540609747771E-3</v>
       </c>
       <c r="AB26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.3078254604113707E-2</v>
       </c>
       <c r="AC26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.1343198855153326E-2</v>
       </c>
       <c r="AD26" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.9081456301046975E-2</v>
       </c>
       <c r="AE26" s="6"/>
       <c r="AF26" s="6">
-        <f t="shared" ref="AF26:AN26" si="27">STDEV(AF4:AF23)</f>
+        <f t="shared" ref="AF26:AN26" si="28">STDEV(AF4:AF23)</f>
         <v>5.5151084352559731E-4</v>
       </c>
       <c r="AG26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.5623591103758885E-4</v>
       </c>
       <c r="AH26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6.122744482664616E-4</v>
       </c>
       <c r="AI26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.0268004210893376E-3</v>
       </c>
       <c r="AJ26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2.4673422735277005E-3</v>
       </c>
       <c r="AK26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.4587147679961276E-3</v>
       </c>
       <c r="AL26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5.1388184109312812E-2</v>
       </c>
       <c r="AM26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1.4316362923886116E-2</v>
       </c>
       <c r="AN26" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5.9079328674071376E-2</v>
       </c>
       <c r="AO26" s="6"/>
       <c r="AP26" s="6">
-        <f t="shared" ref="AP26:AX26" si="28">STDEV(AP4:AP23)</f>
+        <f t="shared" ref="AP26:AX26" si="29">STDEV(AP4:AP23)</f>
         <v>1.4532268993700301E-4</v>
       </c>
       <c r="AQ26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.4545753585442758E-5</v>
       </c>
       <c r="AR26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.5121525264198368E-4</v>
       </c>
       <c r="AS26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.87073437592384E-3</v>
       </c>
       <c r="AT26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4.3206359181076695E-4</v>
       </c>
       <c r="AU26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2.0322802205249256E-3</v>
       </c>
       <c r="AV26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.5249689733579622E-2</v>
       </c>
       <c r="AW26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.2181670992023001E-2</v>
       </c>
       <c r="AX26" s="6">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.8514885440847851E-2</v>
       </c>
       <c r="AY26" s="6"/>
       <c r="AZ26" s="6">
-        <f t="shared" ref="AZ26:BH26" si="29">STDEV(AZ4:AZ23)</f>
+        <f t="shared" ref="AZ26:BH26" si="30">STDEV(AZ4:AZ23)</f>
         <v>1.1789714518216828E-4</v>
       </c>
       <c r="BA26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.5069630922340094E-6</v>
       </c>
       <c r="BB26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.1790272529326431E-4</v>
       </c>
       <c r="BC26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.2732672060775309E-3</v>
       </c>
       <c r="BD26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.9772378672429904E-5</v>
       </c>
       <c r="BE26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.297903095931751E-3</v>
       </c>
       <c r="BF26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.31841261214441791</v>
       </c>
       <c r="BG26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.8381955539976793E-3</v>
       </c>
       <c r="BH26" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.31807106652568956</v>
       </c>
     </row>
@@ -14517,224 +16035,224 @@
         <v>18</v>
       </c>
       <c r="B27" s="7">
-        <f t="shared" ref="B27:J27" si="30">(B26/B25)*100</f>
+        <f t="shared" ref="B27:J27" si="31">(B26/B25)*100</f>
         <v>20.816141222683555</v>
       </c>
       <c r="C27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>25.354888968636075</v>
       </c>
       <c r="D27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21.645657815339472</v>
       </c>
       <c r="E27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8.9840996063651719</v>
       </c>
       <c r="F27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>17.191153481703186</v>
       </c>
       <c r="G27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>10.174888653408551</v>
       </c>
       <c r="H27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3.6835346414753158</v>
       </c>
       <c r="I27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>6.7490155298628505</v>
       </c>
       <c r="J27" s="7">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3.5948228216230853</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7">
-        <f t="shared" ref="L27:T27" si="31">(L26/L25)*100</f>
+        <f t="shared" ref="L27:T27" si="32">(L26/L25)*100</f>
         <v>20.89632540741842</v>
       </c>
       <c r="M27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>9.9110749533297966</v>
       </c>
       <c r="N27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>19.737462364245989</v>
       </c>
       <c r="O27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>2.6042177652254939</v>
       </c>
       <c r="P27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>8.5523514922838668</v>
       </c>
       <c r="Q27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>2.7504978109764382</v>
       </c>
       <c r="R27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.9515807297045853</v>
       </c>
       <c r="S27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.2155357796869695</v>
       </c>
       <c r="T27" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.8272208933844805</v>
       </c>
       <c r="U27" s="7"/>
       <c r="V27" s="7">
-        <f t="shared" ref="V27:AD27" si="32">(V26/V25)*100</f>
+        <f t="shared" ref="V27:AD27" si="33">(V26/V25)*100</f>
         <v>7.8094760891286734</v>
       </c>
       <c r="W27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>14.254350823319722</v>
       </c>
       <c r="X27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.5555013396222321</v>
       </c>
       <c r="Y27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.210394510849639</v>
       </c>
       <c r="Z27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.9745714018161777</v>
       </c>
       <c r="AA27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.666963456126096</v>
       </c>
       <c r="AB27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.97243042634412857</v>
       </c>
       <c r="AC27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>7.5791049045522776</v>
       </c>
       <c r="AD27" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1.0133458373852606</v>
       </c>
       <c r="AE27" s="7"/>
       <c r="AF27" s="7">
-        <f t="shared" ref="AF27:AN27" si="33">(AF26/AF25)*100</f>
+        <f t="shared" ref="AF27:AN27" si="34">(AF26/AF25)*100</f>
         <v>19.99676735045675</v>
       </c>
       <c r="AG27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>177.94160488721451</v>
       </c>
       <c r="AH27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>21.09836141510895</v>
       </c>
       <c r="AI27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.196931712068821</v>
       </c>
       <c r="AJ27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>35.445227316875453</v>
       </c>
       <c r="AK27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.75508721462727</v>
       </c>
       <c r="AL27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.4950544681150062</v>
       </c>
       <c r="AM27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>4.710182080273114</v>
       </c>
       <c r="AN27" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1.5791728753948513</v>
       </c>
       <c r="AO27" s="7"/>
       <c r="AP27" s="7">
-        <f t="shared" ref="AP27:AX27" si="34">(AP26/AP25)*100</f>
+        <f t="shared" ref="AP27:AX27" si="35">(AP26/AP25)*100</f>
         <v>11.148652852857923</v>
       </c>
       <c r="AQ27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>14.122090859653161</v>
       </c>
       <c r="AR27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>10.751173312618818</v>
       </c>
       <c r="AS27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.9148018104001059</v>
       </c>
       <c r="AT27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.7223162075204117</v>
       </c>
       <c r="AU27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.912598577616679</v>
       </c>
       <c r="AV27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>2.0350131812222441</v>
       </c>
       <c r="AW27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>3.6504146583968251</v>
       </c>
       <c r="AX27" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>1.9475565513017594</v>
       </c>
       <c r="AY27" s="7"/>
       <c r="AZ27" s="7">
-        <f t="shared" ref="AZ27:BH27" si="35">(AZ26/AZ25)*100</f>
+        <f t="shared" ref="AZ27:BH27" si="36">(AZ26/AZ25)*100</f>
         <v>1.695264148136721</v>
       </c>
       <c r="BA27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>30.934411244487297</v>
       </c>
       <c r="BB27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.6886669334469251</v>
       </c>
       <c r="BC27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.8388981650681826</v>
       </c>
       <c r="BD27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>2.3009764924749723</v>
       </c>
       <c r="BE27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.8373151362019853</v>
       </c>
       <c r="BF27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.4136814800961526</v>
       </c>
       <c r="BG27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.8211586151529231</v>
       </c>
       <c r="BH27" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>1.4058649726877359</v>
       </c>
     </row>
@@ -14743,224 +16261,224 @@
         <v>14</v>
       </c>
       <c r="B28" s="5">
-        <f t="shared" ref="B28:J28" si="36">MIN(B4:B23)</f>
+        <f t="shared" ref="B28:J28" si="37">MIN(B4:B23)</f>
         <v>4.1900000000000001E-3</v>
       </c>
       <c r="C28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.49E-3</v>
       </c>
       <c r="D28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.6800000000000002E-3</v>
       </c>
       <c r="E28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.25259999999999999</v>
       </c>
       <c r="F28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.4270000000000007E-2</v>
       </c>
       <c r="G28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.34787999999999997</v>
       </c>
       <c r="H28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17.3277</v>
       </c>
       <c r="I28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>6.8286600000000002</v>
       </c>
       <c r="J28" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>24.748380000000001</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5">
-        <f t="shared" ref="L28:T28" si="37">MIN(L4:L23)</f>
+        <f t="shared" ref="L28:T28" si="38">MIN(L4:L23)</f>
         <v>9.8999999999999999E-4</v>
       </c>
       <c r="M28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="N28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>1.08E-3</v>
       </c>
       <c r="O28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4.9869999999999998E-2</v>
       </c>
       <c r="P28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>4.47E-3</v>
       </c>
       <c r="Q28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>5.4349999999999996E-2</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>2.8677299999999999</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.27242</v>
       </c>
       <c r="T28" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>3.1402399999999999</v>
       </c>
       <c r="U28" s="5"/>
       <c r="V28" s="5">
-        <f t="shared" ref="V28:AD28" si="38">MIN(V4:V23)</f>
+        <f t="shared" ref="V28:AD28" si="39">MIN(V4:V23)</f>
         <v>2.2460000000000001E-2</v>
       </c>
       <c r="W28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.82E-3</v>
       </c>
       <c r="X28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>2.4310000000000002E-2</v>
       </c>
       <c r="Y28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.10713</v>
       </c>
       <c r="Z28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>1.8720000000000001E-2</v>
       </c>
       <c r="AA28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.12812999999999999</v>
       </c>
       <c r="AB28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>4.3252100000000002</v>
       </c>
       <c r="AC28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.35034999999999999</v>
       </c>
       <c r="AD28" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>4.7510599999999998</v>
       </c>
       <c r="AE28" s="5"/>
       <c r="AF28" s="5">
-        <f t="shared" ref="AF28:AN28" si="39">MIN(AF4:AF23)</f>
+        <f t="shared" ref="AF28:AN28" si="40">MIN(AF4:AF23)</f>
         <v>2.0899999999999998E-3</v>
       </c>
       <c r="AG28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AH28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2.1900000000000001E-3</v>
       </c>
       <c r="AI28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>6.1800000000000001E-2</v>
       </c>
       <c r="AJ28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2.7599999999999999E-3</v>
       </c>
       <c r="AK28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>6.7239999999999994E-2</v>
       </c>
       <c r="AL28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.3748399999999998</v>
       </c>
       <c r="AM28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.28721999999999998</v>
       </c>
       <c r="AN28" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>3.6624999999999996</v>
       </c>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5">
-        <f t="shared" ref="AP28:AX28" si="40">MIN(AP4:AP23)</f>
+        <f t="shared" ref="AP28:AX28" si="41">MIN(AP4:AP23)</f>
         <v>1.1299999999999999E-3</v>
       </c>
       <c r="AQ28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.0000000000000007E-5</v>
       </c>
       <c r="AR28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>1.2199999999999999E-3</v>
       </c>
       <c r="AS28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6.2350000000000003E-2</v>
       </c>
       <c r="AT28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5.1700000000000001E-3</v>
       </c>
       <c r="AU28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>6.7549999999999999E-2</v>
       </c>
       <c r="AV28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.5780400000000001</v>
       </c>
       <c r="AW28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.31184000000000001</v>
       </c>
       <c r="AX28" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>3.91316</v>
       </c>
       <c r="AY28" s="5"/>
       <c r="AZ28" s="5">
-        <f t="shared" ref="AZ28:BH28" si="41">MIN(AZ4:AZ23)</f>
+        <f t="shared" ref="AZ28:BH28" si="42">MIN(AZ4:AZ23)</f>
         <v>6.7999999999999996E-3</v>
       </c>
       <c r="BA28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>6.8399999999999997E-3</v>
       </c>
       <c r="BC28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.44034000000000001</v>
       </c>
       <c r="BD28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>1.6800000000000001E-3</v>
       </c>
       <c r="BE28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.44208000000000003</v>
       </c>
       <c r="BF28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>22.134399999999999</v>
       </c>
       <c r="BG28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>9.9769999999999998E-2</v>
       </c>
       <c r="BH28" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>22.23631</v>
       </c>
     </row>
@@ -14969,224 +16487,224 @@
         <v>15</v>
       </c>
       <c r="B29" s="5">
-        <f t="shared" ref="B29:J29" si="42">MAX(B4:B23)</f>
+        <f t="shared" ref="B29:J29" si="43">MAX(B4:B23)</f>
         <v>7.5199999999999998E-3</v>
       </c>
       <c r="C29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.9099999999999998E-3</v>
       </c>
       <c r="D29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>1.0249999999999999E-2</v>
       </c>
       <c r="E29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.35021999999999998</v>
       </c>
       <c r="F29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.16083</v>
       </c>
       <c r="G29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.50252999999999992</v>
       </c>
       <c r="H29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>20.15898</v>
       </c>
       <c r="I29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>8.6584099999999999</v>
       </c>
       <c r="J29" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>28.81739</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5">
-        <f t="shared" ref="L29:T29" si="43">MAX(L4:L23)</f>
+        <f t="shared" ref="L29:T29" si="44">MAX(L4:L23)</f>
         <v>1.89E-3</v>
       </c>
       <c r="M29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.1E-4</v>
       </c>
       <c r="N29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>1.99E-3</v>
       </c>
       <c r="O29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>5.4620000000000002E-2</v>
       </c>
       <c r="P29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>6.0099999999999997E-3</v>
       </c>
       <c r="Q29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>5.9710000000000006E-2</v>
       </c>
       <c r="R29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>3.0706699999999998</v>
       </c>
       <c r="S29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.28234999999999999</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>3.3521299999999998</v>
       </c>
       <c r="U29" s="5"/>
       <c r="V29" s="5">
-        <f t="shared" ref="V29:AD29" si="44">MAX(V4:V23)</f>
+        <f t="shared" ref="V29:AD29" si="45">MAX(V4:V23)</f>
         <v>3.1309999999999998E-2</v>
       </c>
       <c r="W29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>3.0599999999999998E-3</v>
       </c>
       <c r="X29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>3.3439999999999998E-2</v>
       </c>
       <c r="Y29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.13588</v>
       </c>
       <c r="Z29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.2290000000000001E-2</v>
       </c>
       <c r="AA29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.15736</v>
       </c>
       <c r="AB29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>4.5352399999999999</v>
       </c>
       <c r="AC29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>0.47299000000000002</v>
       </c>
       <c r="AD29" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>4.9641999999999999</v>
       </c>
       <c r="AE29" s="5"/>
       <c r="AF29" s="5">
-        <f t="shared" ref="AF29:AN29" si="45">MAX(AF4:AF23)</f>
+        <f t="shared" ref="AF29:AN29" si="46">MAX(AF4:AF23)</f>
         <v>3.9699999999999996E-3</v>
       </c>
       <c r="AG29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="AH29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>4.0699999999999998E-3</v>
       </c>
       <c r="AI29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.10231</v>
       </c>
       <c r="AJ29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.393E-2</v>
       </c>
       <c r="AK29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.10979</v>
       </c>
       <c r="AL29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>3.5969199999999999</v>
       </c>
       <c r="AM29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.33407999999999999</v>
       </c>
       <c r="AN29" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>3.91554</v>
       </c>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5">
-        <f t="shared" ref="AP29:AX29" si="46">MAX(AP4:AP23)</f>
+        <f t="shared" ref="AP29:AX29" si="47">MAX(AP4:AP23)</f>
         <v>1.6900000000000001E-3</v>
       </c>
       <c r="AQ29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1.3999999999999999E-4</v>
       </c>
       <c r="AR29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1.8000000000000002E-3</v>
       </c>
       <c r="AS29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7.0230000000000001E-2</v>
       </c>
       <c r="AT29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6.6699999999999997E-3</v>
       </c>
       <c r="AU29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7.5759999999999994E-2</v>
       </c>
       <c r="AV29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>3.8773</v>
       </c>
       <c r="AW29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.35949999999999999</v>
       </c>
       <c r="AX29" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>4.2269899999999998</v>
       </c>
       <c r="AY29" s="5"/>
       <c r="AZ29" s="5">
-        <f t="shared" ref="AZ29:BH29" si="47">MAX(AZ4:AZ23)</f>
+        <f t="shared" ref="AZ29:BH29" si="48">MAX(AZ4:AZ23)</f>
         <v>7.1799999999999998E-3</v>
       </c>
       <c r="BA29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>4.0000000000000003E-5</v>
       </c>
       <c r="BB29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>7.1999999999999998E-3</v>
       </c>
       <c r="BC29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.46969</v>
       </c>
       <c r="BD29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1.83E-3</v>
       </c>
       <c r="BE29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.47148000000000001</v>
       </c>
       <c r="BF29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.4633</v>
       </c>
       <c r="BG29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.10732</v>
       </c>
       <c r="BH29" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.564140000000002</v>
       </c>
     </row>
@@ -15195,224 +16713,224 @@
         <v>19</v>
       </c>
       <c r="B30" s="6">
-        <f t="shared" ref="B30:J30" si="48">B29-B28</f>
+        <f t="shared" ref="B30:J30" si="49">B29-B28</f>
         <v>3.3299999999999996E-3</v>
       </c>
       <c r="C30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.4199999999999998E-3</v>
       </c>
       <c r="D30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>4.5699999999999985E-3</v>
       </c>
       <c r="E30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>9.7619999999999985E-2</v>
       </c>
       <c r="F30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>6.6559999999999994E-2</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.15464999999999995</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>2.8312799999999996</v>
       </c>
       <c r="I30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>1.8297499999999998</v>
       </c>
       <c r="J30" s="6">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>4.0690099999999987</v>
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="6">
-        <f t="shared" ref="L30:T30" si="49">L29-L28</f>
+        <f t="shared" ref="L30:T30" si="50">L29-L28</f>
         <v>8.9999999999999998E-4</v>
       </c>
       <c r="M30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>2.9999999999999997E-5</v>
       </c>
       <c r="N30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>9.1E-4</v>
       </c>
       <c r="O30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>4.7500000000000042E-3</v>
       </c>
       <c r="P30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>1.5399999999999997E-3</v>
       </c>
       <c r="Q30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>5.3600000000000106E-3</v>
       </c>
       <c r="R30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.2029399999999999</v>
       </c>
       <c r="S30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>9.9299999999999944E-3</v>
       </c>
       <c r="T30" s="6">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.21188999999999991</v>
       </c>
       <c r="U30" s="6"/>
       <c r="V30" s="6">
-        <f t="shared" ref="V30:AD30" si="50">V29-V28</f>
+        <f t="shared" ref="V30:AD30" si="51">V29-V28</f>
         <v>8.8499999999999968E-3</v>
       </c>
       <c r="W30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.2399999999999998E-3</v>
       </c>
       <c r="X30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>9.1299999999999958E-3</v>
       </c>
       <c r="Y30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>2.8749999999999998E-2</v>
       </c>
       <c r="Z30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>3.5700000000000003E-3</v>
       </c>
       <c r="AA30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>2.9230000000000006E-2</v>
       </c>
       <c r="AB30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.21002999999999972</v>
       </c>
       <c r="AC30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.12264000000000003</v>
       </c>
       <c r="AD30" s="6">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.21314000000000011</v>
       </c>
       <c r="AE30" s="6"/>
       <c r="AF30" s="6">
-        <f t="shared" ref="AF30:AN30" si="51">AF29-AF28</f>
+        <f t="shared" ref="AF30:AN30" si="52">AF29-AF28</f>
         <v>1.8799999999999997E-3</v>
       </c>
       <c r="AG30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>5.9999999999999995E-4</v>
       </c>
       <c r="AH30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.8799999999999997E-3</v>
       </c>
       <c r="AI30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.0509999999999997E-2</v>
       </c>
       <c r="AJ30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>1.1169999999999999E-2</v>
       </c>
       <c r="AK30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.2550000000000004E-2</v>
       </c>
       <c r="AL30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.22208000000000006</v>
       </c>
       <c r="AM30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>4.6860000000000013E-2</v>
       </c>
       <c r="AN30" s="6">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.25304000000000038</v>
       </c>
       <c r="AO30" s="6"/>
       <c r="AP30" s="6">
-        <f t="shared" ref="AP30:AX30" si="52">AP29-AP28</f>
+        <f t="shared" ref="AP30:AX30" si="53">AP29-AP28</f>
         <v>5.6000000000000017E-4</v>
       </c>
       <c r="AQ30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.9999999999999981E-5</v>
       </c>
       <c r="AR30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.8000000000000022E-4</v>
       </c>
       <c r="AS30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>7.8799999999999981E-3</v>
       </c>
       <c r="AT30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>1.4999999999999996E-3</v>
       </c>
       <c r="AU30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>8.2099999999999951E-3</v>
       </c>
       <c r="AV30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.29925999999999986</v>
       </c>
       <c r="AW30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>4.765999999999998E-2</v>
       </c>
       <c r="AX30" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.31382999999999983</v>
       </c>
       <c r="AY30" s="6"/>
       <c r="AZ30" s="6">
-        <f t="shared" ref="AZ30:BH30" si="53">AZ29-AZ28</f>
+        <f t="shared" ref="AZ30:BH30" si="54">AZ29-AZ28</f>
         <v>3.8000000000000013E-4</v>
       </c>
       <c r="BA30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="BB30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>3.6000000000000008E-4</v>
       </c>
       <c r="BC30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>2.9349999999999987E-2</v>
       </c>
       <c r="BD30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.4999999999999996E-4</v>
       </c>
       <c r="BE30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>2.9399999999999982E-2</v>
       </c>
       <c r="BF30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.3289000000000009</v>
       </c>
       <c r="BG30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>7.5500000000000012E-3</v>
       </c>
       <c r="BH30" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.3278300000000023</v>
       </c>
     </row>
@@ -15437,11 +16955,11 @@
         <v>1.6170979381443303E-2</v>
       </c>
       <c r="F31" s="6">
-        <f t="shared" ref="F31:G31" si="54">F25/19.4</f>
+        <f t="shared" ref="F31:G31" si="55">F25/19.4</f>
         <v>6.7799742268041252E-3</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.2950953608247428E-2</v>
       </c>
       <c r="H31" s="6">
@@ -15449,11 +16967,11 @@
         <v>1.6599892920353986E-2</v>
       </c>
       <c r="I31" s="6">
-        <f t="shared" ref="I31:J31" si="55">I25/1130</f>
+        <f t="shared" ref="I31:J31" si="56">I25/1130</f>
         <v>6.9472035398230091E-3</v>
       </c>
       <c r="J31" s="6">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>2.3547096460176994E-2</v>
       </c>
       <c r="K31" s="6"/>
@@ -15478,7 +16996,7 @@
         <v>2.5250000000000001E-4</v>
       </c>
       <c r="Q31" s="6">
-        <f t="shared" ref="Q31" si="56">Q25/19.4</f>
+        <f t="shared" ref="Q31" si="57">Q25/19.4</f>
         <v>2.9402577319587635E-3</v>
       </c>
       <c r="R31" s="6">
@@ -15511,11 +17029,11 @@
         <v>6.1899226804123719E-3</v>
       </c>
       <c r="Z31" s="6">
-        <f t="shared" ref="Z31:AA31" si="57">Z25/19.4</f>
+        <f t="shared" ref="Z31:AA31" si="58">Z25/19.4</f>
         <v>1.0593814432989692E-3</v>
       </c>
       <c r="AA31" s="6">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>7.2493041237113405E-3</v>
       </c>
       <c r="AB31" s="6">
@@ -15523,11 +17041,11 @@
         <v>3.9203163716814166E-3</v>
       </c>
       <c r="AC31" s="6">
-        <f t="shared" ref="AC31:AD31" si="58">AC25/1130</f>
+        <f t="shared" ref="AC31:AD31" si="59">AC25/1130</f>
         <v>3.6597123893805308E-4</v>
       </c>
       <c r="AD31" s="6">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>4.2862876106194697E-3</v>
       </c>
       <c r="AE31" s="6"/>
@@ -15548,11 +17066,11 @@
         <v>3.6952319587628874E-3</v>
       </c>
       <c r="AJ31" s="6">
-        <f t="shared" ref="AJ31:AK31" si="59">AJ25/19.4</f>
+        <f t="shared" ref="AJ31:AK31" si="60">AJ25/19.4</f>
         <v>3.5881443298969076E-4</v>
       </c>
       <c r="AK31" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4.0540463917525778E-3</v>
       </c>
       <c r="AL31" s="6">
@@ -15560,11 +17078,11 @@
         <v>3.0417800884955746E-3</v>
       </c>
       <c r="AM31" s="6">
-        <f t="shared" ref="AM31:AN31" si="60">AM25/1130</f>
+        <f t="shared" ref="AM31:AN31" si="61">AM25/1130</f>
         <v>2.6897787610619464E-4</v>
       </c>
       <c r="AN31" s="6">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>3.3107579646017697E-3</v>
       </c>
       <c r="AO31" s="6"/>
@@ -15585,11 +17103,11 @@
         <v>3.3082731958762892E-3</v>
       </c>
       <c r="AT31" s="6">
-        <f t="shared" ref="AT31:AU31" si="61">AT25/19.4</f>
+        <f t="shared" ref="AT31:AU31" si="62">AT25/19.4</f>
         <v>2.8840206185567005E-4</v>
       </c>
       <c r="AU31" s="6">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>3.5966752577319587E-3</v>
       </c>
       <c r="AV31" s="6">
@@ -15597,11 +17115,11 @@
         <v>3.2723446902654862E-3</v>
       </c>
       <c r="AW31" s="6">
-        <f t="shared" ref="AW31:AX31" si="62">AW25/1130</f>
+        <f t="shared" ref="AW31:AX31" si="63">AW25/1130</f>
         <v>2.9531548672566367E-4</v>
       </c>
       <c r="AX31" s="6">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>3.5676601769911499E-3</v>
       </c>
       <c r="AY31" s="6"/>
@@ -15622,11 +17140,11 @@
         <v>2.3190902061855673E-2</v>
       </c>
       <c r="BD31" s="6">
-        <f t="shared" ref="BD31:BE31" si="63">BD25/19.4</f>
+        <f t="shared" ref="BD31:BE31" si="64">BD25/19.4</f>
         <v>8.9097938144329912E-5</v>
       </c>
       <c r="BE31" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>2.3280000000000002E-2</v>
       </c>
       <c r="BF31" s="6">
@@ -15634,22 +17152,29 @@
         <v>1.9932430088495576E-2</v>
       </c>
       <c r="BG31" s="6">
-        <f t="shared" ref="BG31:BH31" si="64">BG25/1130</f>
+        <f t="shared" ref="BG31:BH31" si="65">BG25/1130</f>
         <v>8.9323451327433649E-5</v>
       </c>
       <c r="BH31" s="6">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>2.0021753539823009E-2</v>
       </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37">
+      <c r="A37" s="8">
         <v>8760</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="8">
         <v>525600</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="8">
         <v>31536000</v>
       </c>
     </row>
